--- a/assets/data/invitados.xlsx
+++ b/assets/data/invitados.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="147">
   <si>
     <t>id</t>
   </si>
@@ -38,214 +38,430 @@
     <t>pases</t>
   </si>
   <si>
+    <t>c4ca4238a0b923820dcc509a6f75849b</t>
+  </si>
+  <si>
     <t>OSCAR GONZALEZ  HERNANDEZ</t>
   </si>
   <si>
+    <t>c81e728d9d4c2f636f067f89cc14862c</t>
+  </si>
+  <si>
     <t xml:space="preserve">FAM. GONZALEZ GUZMAN </t>
   </si>
   <si>
+    <t>eccbc87e4b5ce2fe28308fd9f2a7baf3</t>
+  </si>
+  <si>
     <t>FAM. AYALA MUÑOZ</t>
   </si>
   <si>
+    <t>a87ff679a2f3e71d9181a67b7542122c</t>
+  </si>
+  <si>
     <t>FAM. MUÑOZ AGUILAR</t>
   </si>
   <si>
+    <t>e4da3b7fbbce2345d7772b0674a318d5</t>
+  </si>
+  <si>
     <t>FAM. SANCHEZ MUÑOZ</t>
   </si>
   <si>
+    <t>1679091c5a880faf6fb5e6087eb1b2dc</t>
+  </si>
+  <si>
     <t>FAM.HERNANDEZ HERNANDEZ</t>
   </si>
   <si>
+    <t>8f14e45fceea167a5a36dedd4bea2543</t>
+  </si>
+  <si>
     <t>FAM. RAMOS HERNANDEZ</t>
   </si>
   <si>
+    <t>c9f0f895fb98ab9159f51fd0297e236d</t>
+  </si>
+  <si>
     <t>FAM. JIMENEZ HERNANDEZ</t>
   </si>
   <si>
+    <t>45c48cce2e2d7fbdea1afc51c7c6ad26</t>
+  </si>
+  <si>
     <t>FAM.HERNANDEZ NERIA</t>
   </si>
   <si>
+    <t>d3d9446802a44259755d38e6d163e820</t>
+  </si>
+  <si>
     <t>DAVID RUIZ Y FAMILIA</t>
   </si>
   <si>
+    <t>6512bd43d9caa6e02c990b0a82652dca</t>
+  </si>
+  <si>
     <t>CESAR RUIZ</t>
   </si>
   <si>
+    <t>c20ad4d76fe97759aa27a0c99bff6710</t>
+  </si>
+  <si>
     <t>LUIS Y FAMILIA</t>
   </si>
   <si>
+    <t>c51ce410c124a10e0db5e4b97fc2af39</t>
+  </si>
+  <si>
     <t>FAM. LOPEZ MERCADO</t>
   </si>
   <si>
+    <t>aab3238922bcc25a6f606eb525ffdc56</t>
+  </si>
+  <si>
     <t>JORGE RAMOS HERNANDEZ</t>
   </si>
   <si>
+    <t>9bf31c7ff062936a96d3c8bd1f8f2ff3</t>
+  </si>
+  <si>
     <t>FAM. RAMOS MELENDEZ</t>
   </si>
   <si>
+    <t>c74d97b01eae257e44aa9d5bade97baf</t>
+  </si>
+  <si>
     <t>FAM.RIOS HERNANDEZ</t>
   </si>
   <si>
+    <t>70efdf2ec9b086079795c442636b55fb</t>
+  </si>
+  <si>
     <t>FAM. PAVON MARTINEZ</t>
   </si>
   <si>
+    <t>6f4922f45568161a8cdf4ad2299f6d23</t>
+  </si>
+  <si>
     <t>SOFI CRUZ</t>
   </si>
   <si>
+    <t>1f0e3dad99908345f7439f8ffabdffc4</t>
+  </si>
+  <si>
     <t>FAM. MELENDEZ SILVA</t>
   </si>
   <si>
+    <t>98f13708210194c475687be6106a3b84</t>
+  </si>
+  <si>
     <t>FAM. MELENDEZ LOPEZ</t>
   </si>
   <si>
+    <t>3c59dc048e8850243be8079a5c74d079</t>
+  </si>
+  <si>
     <t>FERNANDA</t>
   </si>
   <si>
+    <t>b6d767d2f8ed5d21a44b0e5886680cb9</t>
+  </si>
+  <si>
     <t>MIA</t>
   </si>
   <si>
+    <t>37693cfc748049e45d87b8c7d8b9aacd</t>
+  </si>
+  <si>
     <t>SUZETTE</t>
   </si>
   <si>
+    <t>1ff1de774005f8da13f42943881c655f</t>
+  </si>
+  <si>
     <t>MELISA</t>
   </si>
   <si>
+    <t>8e296a067a37563370ded05f5a3bf3ec</t>
+  </si>
+  <si>
     <t>SANTIAGO M</t>
   </si>
   <si>
+    <t>4e732ced3463d06de0ca9a15b6153677</t>
+  </si>
+  <si>
     <t>OSCAR</t>
   </si>
   <si>
+    <t>02e74f10e0327ad868d138f2b4fdd6f0</t>
+  </si>
+  <si>
     <t>RONIEL</t>
   </si>
   <si>
+    <t>33e75ff09dd601bbe69f351039152189</t>
+  </si>
+  <si>
     <t>AURELIO</t>
   </si>
   <si>
+    <t>6ea9ab1baa0efb9e19094440c317e21b</t>
+  </si>
+  <si>
     <t>XIMENA CALLEJA</t>
   </si>
   <si>
+    <t>34173cb38f07f89ddbebc2ac9128303f</t>
+  </si>
+  <si>
     <t>AIME</t>
   </si>
   <si>
+    <t>c16a5320fa475530d9583c34fd356ef5</t>
+  </si>
+  <si>
     <t>NANCI</t>
   </si>
   <si>
+    <t>6364d3f0f495b6ab9dcf8d3b5c6e0b01</t>
+  </si>
+  <si>
     <t>JESUS</t>
   </si>
   <si>
+    <t>182be0c5cdcd5072bb1864cdee4d3d6e</t>
+  </si>
+  <si>
     <t>JOSE</t>
   </si>
   <si>
+    <t>e369853df766fa44e1ed0ff613f563bd</t>
+  </si>
+  <si>
     <t>SEBASTIAN</t>
   </si>
   <si>
+    <t>1c383cd30b7c298ab50293adfecb7b18</t>
+  </si>
+  <si>
     <t>YULI</t>
   </si>
   <si>
+    <t>19ca14e7ea6328a42e0eb13d585e4c22</t>
+  </si>
+  <si>
     <t>CESAR</t>
   </si>
   <si>
+    <t>a5bfc9e07964f8dddeb95fc584cd965d</t>
+  </si>
+  <si>
     <t>FAM. PINACHO MORENO</t>
   </si>
   <si>
+    <t>a5771bce93e200c36f7cd9dfd0e5deaa</t>
+  </si>
+  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
+    <t>d67d8ab4f4c10bf22aa353e27879133c</t>
+  </si>
+  <si>
     <t>ALDAHIR</t>
   </si>
   <si>
+    <t>d645920e395fedad7bbbed0eca3fe2e0</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
+    <t>3416a75f4cea9109507cacd8e2f2aefc</t>
+  </si>
+  <si>
     <t>MITZI</t>
   </si>
   <si>
+    <t>a1d0c6e83f027327d8461063f4ac58a6</t>
+  </si>
+  <si>
     <t>HELEN</t>
   </si>
   <si>
+    <t>17e62166fc8586dfa4d1bc0e1742c08b</t>
+  </si>
+  <si>
     <t>CAMILA</t>
   </si>
   <si>
+    <t>f7177163c833dff4b38fc8d2872f1ec6</t>
+  </si>
+  <si>
     <t>ALISON</t>
   </si>
   <si>
+    <t>6c8349cc7260ae62e3b1396831a8398f</t>
+  </si>
+  <si>
     <t>FAM.AGUIRRE  GARNICA</t>
   </si>
   <si>
+    <t>d9d4f495e875a2e075a1a4a6e1b9770f</t>
+  </si>
+  <si>
     <t>FAM.SIGUENZA GALICIA</t>
   </si>
   <si>
+    <t>67c6a1e7ce56d3d6fa748ab6d9af3fd7</t>
+  </si>
+  <si>
     <t>MARITZA MENDOZA Y FAM.</t>
   </si>
   <si>
+    <t>642e92efb79421734881b53e1e1b18b6</t>
+  </si>
+  <si>
     <t>FAM. MENDOZA BENITEZ</t>
   </si>
   <si>
+    <t>f457c545a9ded88f18ecee47145a72c0</t>
+  </si>
+  <si>
     <t>FAM. DURAN ARGUELLES</t>
   </si>
   <si>
+    <t>c0c7c76d30bd3dcaefc96f40275bdc0a</t>
+  </si>
+  <si>
     <t>FAM. LEYRA GONZALEZ</t>
   </si>
   <si>
+    <t>2838023a778dfaecdc212708f721b788</t>
+  </si>
+  <si>
     <t>LAURA</t>
   </si>
   <si>
+    <t>9a1158154dfa42caddbd0694a4e9bdc8</t>
+  </si>
+  <si>
     <t>SAMANTA</t>
   </si>
   <si>
+    <t>d82c8d1619ad8176d665453cfb2e55f0</t>
+  </si>
+  <si>
     <t xml:space="preserve">SABRINA </t>
   </si>
   <si>
+    <t>a684eceee76fc522773286a895bc8436</t>
+  </si>
+  <si>
     <t>TZINTLI</t>
   </si>
   <si>
+    <t>b53b3a3d6ab90ce0268229151c9bde11</t>
+  </si>
+  <si>
     <t>RAZIEL</t>
   </si>
   <si>
+    <t>9f61408e3afb633e50cdf1b20de6f466</t>
+  </si>
+  <si>
     <t>YAEL</t>
   </si>
   <si>
+    <t>72b32a1f754ba1c09b3695e0cb6cde7f</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>66f041e16a60928b05a7e228a89c3799</t>
+  </si>
+  <si>
     <t>DANIEL</t>
   </si>
   <si>
+    <t>093f65e080a295f8076b1c5722a46aa2</t>
+  </si>
+  <si>
     <t xml:space="preserve">BRANDON </t>
   </si>
   <si>
+    <t>072b030ba126b2f4b2374f342be9ed44</t>
+  </si>
+  <si>
     <t>FRIDA</t>
   </si>
   <si>
+    <t>7f39f8317fbdb1988ef4c628eba02591</t>
+  </si>
+  <si>
     <t>MONTSE</t>
   </si>
   <si>
+    <t>44f683a84163b3523afe57c2e008bc8c</t>
+  </si>
+  <si>
     <t>YADIRA</t>
   </si>
   <si>
+    <t>03afdbd66e7929b125f8597834fa83a4</t>
+  </si>
+  <si>
     <t>LIZ</t>
   </si>
   <si>
+    <t>ea5d2f1c4608232e07d3aa3d998e5135</t>
+  </si>
+  <si>
     <t>ENYA</t>
   </si>
   <si>
+    <t>fc490ca45c00b1249bbe3554a4fdf6fb</t>
+  </si>
+  <si>
+    <t>3295c76acbf4caaed33c36b1b5fc2cb1</t>
+  </si>
+  <si>
     <t>GERARDO</t>
   </si>
   <si>
+    <t>735b90b4568125ed6c3f678819b6e058</t>
+  </si>
+  <si>
     <t>JORGE</t>
   </si>
   <si>
+    <t>a3f390d88e4c41f2747bfa2f1b5f87db</t>
+  </si>
+  <si>
     <t>MARGARITA FLORES</t>
   </si>
   <si>
+    <t>14bfa6bb14875e45bba028a21ed38046</t>
+  </si>
+  <si>
     <t>ANA FLORES</t>
   </si>
   <si>
+    <t>7cbbc409ec990f19c78c75bd1e06f215</t>
+  </si>
+  <si>
     <t>DIEGO FLORES</t>
   </si>
   <si>
+    <t>e2c420d928d4bf8ce0ff2ec19b371514</t>
+  </si>
+  <si>
     <t>FAM. FLORES SARTORIUS</t>
+  </si>
+  <si>
+    <t>32bb90e8976aab5298d5da10fe66f21d</t>
   </si>
   <si>
     <t>ROQUE LUIS Y FAMILIA</t>
@@ -264,7 +480,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -274,13 +490,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -431,7 +640,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -495,12 +704,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -755,148 +958,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1231,7 +1434,7 @@
   <dimension ref="A1:C74"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="11.4285714285714" style="1"/>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.4285714285714" customWidth="1"/>
     <col min="3" max="3" width="9.85714285714286" style="1" customWidth="1"/>
     <col min="5" max="5" width="11.8571428571429" customWidth="1"/>
@@ -1249,803 +1452,803 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>1</v>
+      <c r="A2" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1">
-        <v>2</v>
+      <c r="A3" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1">
-        <v>3</v>
+      <c r="A4" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1">
-        <v>4</v>
+      <c r="A5" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1">
-        <v>5</v>
+      <c r="A6" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="1">
-        <v>6</v>
+      <c r="A7" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="1">
-        <v>7</v>
+      <c r="A8" t="s">
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="1">
-        <v>8</v>
+      <c r="A9" t="s">
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C9" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="1">
-        <v>9</v>
+      <c r="A10" t="s">
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="1">
-        <v>10</v>
+      <c r="A11" t="s">
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="1">
-        <v>11</v>
+      <c r="A12" t="s">
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="1">
-        <v>12</v>
+      <c r="A13" t="s">
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C13" s="1">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="1">
-        <v>13</v>
+      <c r="A14" t="s">
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="1">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="1">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="1">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="1">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="1">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="1">
-        <v>19</v>
+      <c r="A20" t="s">
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="1">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="22" ht="15.75" spans="1:3">
-      <c r="A22" s="1">
-        <v>21</v>
+      <c r="A22" t="s">
+        <v>43</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="23" ht="15.75" spans="1:3">
-      <c r="A23" s="1">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>45</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C23" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="24" ht="15.75" spans="1:3">
-      <c r="A24" s="1">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>47</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C24" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="25" ht="15.75" spans="1:3">
-      <c r="A25" s="1">
-        <v>24</v>
+      <c r="A25" t="s">
+        <v>49</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C25" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="26" ht="15.75" spans="1:3">
-      <c r="A26" s="1">
-        <v>25</v>
+      <c r="A26" t="s">
+        <v>51</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C26" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="27" ht="15.75" spans="1:3">
-      <c r="A27" s="1">
-        <v>26</v>
+      <c r="A27" t="s">
+        <v>53</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C27" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="28" ht="15.75" spans="1:3">
-      <c r="A28" s="1">
-        <v>27</v>
+      <c r="A28" t="s">
+        <v>55</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="C28" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="29" ht="15.75" spans="1:3">
-      <c r="A29" s="1">
-        <v>28</v>
+      <c r="A29" t="s">
+        <v>57</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C29" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="30" ht="15.75" spans="1:3">
-      <c r="A30" s="1">
-        <v>29</v>
+      <c r="A30" t="s">
+        <v>59</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
       <c r="C30" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="31" ht="15.75" spans="1:3">
-      <c r="A31" s="1">
-        <v>30</v>
+      <c r="A31" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C31" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="32" ht="15.75" spans="1:3">
-      <c r="A32" s="1">
-        <v>31</v>
+      <c r="A32" t="s">
+        <v>63</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="C32" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="33" ht="15.75" spans="1:3">
-      <c r="A33" s="1">
-        <v>32</v>
+      <c r="A33" t="s">
+        <v>65</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="C33" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="34" ht="15.75" spans="1:3">
-      <c r="A34" s="1">
-        <v>33</v>
+      <c r="A34" t="s">
+        <v>67</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="C34" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="35" ht="15.75" spans="1:3">
-      <c r="A35" s="1">
-        <v>34</v>
+      <c r="A35" t="s">
+        <v>69</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="C35" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="36" ht="15.75" spans="1:3">
-      <c r="A36" s="1">
-        <v>35</v>
+      <c r="A36" t="s">
+        <v>71</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="C36" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="37" ht="15.75" spans="1:3">
-      <c r="A37" s="1">
-        <v>36</v>
+      <c r="A37" t="s">
+        <v>73</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="C37" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="38" ht="15.75" spans="1:3">
-      <c r="A38" s="1">
-        <v>37</v>
+      <c r="A38" t="s">
+        <v>75</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3">
-      <c r="A39" s="1">
-        <v>38</v>
+      <c r="A39" t="s">
+        <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="C39" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3">
-      <c r="A40" s="1">
-        <v>39</v>
+      <c r="A40" t="s">
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C40" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3">
-      <c r="A41" s="1">
-        <v>40</v>
+      <c r="A41" t="s">
+        <v>81</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="C41" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="1">
-        <v>41</v>
+      <c r="A42" t="s">
+        <v>83</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C42" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="1">
-        <v>42</v>
+      <c r="A43" t="s">
+        <v>85</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C43" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3">
-      <c r="A44" s="1">
-        <v>43</v>
+      <c r="A44" t="s">
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>88</v>
       </c>
       <c r="C44" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3">
-      <c r="A45" s="1">
-        <v>44</v>
+      <c r="A45" t="s">
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="C45" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3">
-      <c r="A46" s="1">
-        <v>45</v>
+      <c r="A46" t="s">
+        <v>91</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="C46" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3">
-      <c r="A47" s="1">
-        <v>46</v>
+      <c r="A47" t="s">
+        <v>93</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="C47" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:3">
-      <c r="A48" s="1">
-        <v>47</v>
+      <c r="A48" t="s">
+        <v>95</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C48" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3">
-      <c r="A49" s="1">
-        <v>48</v>
+      <c r="A49" t="s">
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="C49" s="1">
         <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:3">
-      <c r="A50" s="1">
-        <v>49</v>
+      <c r="A50" t="s">
+        <v>99</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="C50" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3">
-      <c r="A51" s="1">
-        <v>50</v>
+      <c r="A51" t="s">
+        <v>101</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="C51" s="1">
         <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:3">
-      <c r="A52" s="1">
-        <v>51</v>
+      <c r="A52" t="s">
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C52" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:3">
-      <c r="A53" s="1">
-        <v>52</v>
+      <c r="A53" t="s">
+        <v>105</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C53" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="1">
-        <v>53</v>
+      <c r="A54" t="s">
+        <v>107</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>108</v>
       </c>
       <c r="C54" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3">
-      <c r="A55" s="1">
-        <v>54</v>
+      <c r="A55" t="s">
+        <v>109</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="C55" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3">
-      <c r="A56" s="1">
-        <v>55</v>
+      <c r="A56" t="s">
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>112</v>
       </c>
       <c r="C56" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3">
-      <c r="A57" s="1">
-        <v>56</v>
+      <c r="A57" t="s">
+        <v>113</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>114</v>
       </c>
       <c r="C57" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3">
-      <c r="A58" s="1">
-        <v>57</v>
+      <c r="A58" t="s">
+        <v>115</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>116</v>
       </c>
       <c r="C58" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3">
-      <c r="A59" s="1">
-        <v>58</v>
+      <c r="A59" t="s">
+        <v>117</v>
       </c>
       <c r="B59" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3">
-      <c r="A60" s="1">
-        <v>59</v>
+      <c r="A60" t="s">
+        <v>119</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="C60" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="1">
-        <v>60</v>
+      <c r="A61" t="s">
+        <v>121</v>
       </c>
       <c r="B61" t="s">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="C61" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="1">
-        <v>61</v>
+      <c r="A62" t="s">
+        <v>123</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C62" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="1">
-        <v>62</v>
+      <c r="A63" t="s">
+        <v>125</v>
       </c>
       <c r="B63" t="s">
-        <v>64</v>
+        <v>126</v>
       </c>
       <c r="C63" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3">
-      <c r="A64" s="1">
-        <v>63</v>
+      <c r="A64" t="s">
+        <v>127</v>
       </c>
       <c r="B64" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="C64" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="1">
-        <v>64</v>
+      <c r="A65" t="s">
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>66</v>
+        <v>130</v>
       </c>
       <c r="C65" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3">
-      <c r="A66" s="1">
-        <v>65</v>
+      <c r="A66" t="s">
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>60</v>
+        <v>118</v>
       </c>
       <c r="C66" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="1">
-        <v>66</v>
+      <c r="A67" t="s">
+        <v>132</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>133</v>
       </c>
       <c r="C67" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="1">
-        <v>67</v>
+      <c r="A68" t="s">
+        <v>134</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="C68" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3">
-      <c r="A69" s="1">
-        <v>68</v>
+      <c r="A69" t="s">
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
       <c r="C69" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="1">
-        <v>69</v>
+      <c r="A70" t="s">
+        <v>138</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="C70" s="1">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="1">
-        <v>70</v>
+      <c r="A71" t="s">
+        <v>140</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="C71" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3">
-      <c r="A72" s="1">
-        <v>71</v>
+      <c r="A72" t="s">
+        <v>142</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>143</v>
       </c>
       <c r="C72" s="1">
         <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:3">
-      <c r="A73" s="1">
-        <v>72</v>
+      <c r="A73" t="s">
+        <v>144</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="C73" s="1">
         <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:3">
-      <c r="A74" s="1">
-        <v>73</v>
+      <c r="A74" t="s">
+        <v>144</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="C74" s="1">
         <v>3</v>

--- a/assets/data/invitados.xlsx
+++ b/assets/data/invitados.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="11460"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="203">
   <si>
     <t>id</t>
   </si>
@@ -467,7 +467,175 @@
     <t>ROQUE LUIS Y FAMILIA</t>
   </si>
   <si>
+    <t>d2ddea18f00665ce8623e36bd4e3c7c5</t>
+  </si>
+  <si>
     <t>FAM. MACHUCA LOPEZ</t>
+  </si>
+  <si>
+    <t>f899139df5e1059396431415e770c6dd</t>
+  </si>
+  <si>
+    <t>FAM. MUÑOZ GALICIA</t>
+  </si>
+  <si>
+    <t>38b3eff8baf56627478ec76a704e9b52</t>
+  </si>
+  <si>
+    <t>FAM. MUÑOZ ALVAREZ</t>
+  </si>
+  <si>
+    <t>ce5140df15d046a66883807d18d0264b</t>
+  </si>
+  <si>
+    <t>FAM.SANCHEZ GONZALEZ</t>
+  </si>
+  <si>
+    <t>21adaaa0164a4a9a8e42e6996b19e46b</t>
+  </si>
+  <si>
+    <t>FAM. PEREZ HERNANDEZ</t>
+  </si>
+  <si>
+    <t>758bb6da541da15810094d81d1ba4728</t>
+  </si>
+  <si>
+    <t>FAM. HERNANDEZ LUCHI</t>
+  </si>
+  <si>
+    <t>fa894ef0af4d114f991f029171f38547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM. LOPEZ HERANDEZ </t>
+  </si>
+  <si>
+    <t>73f24517cf9334dab2de8279abfca6d6</t>
+  </si>
+  <si>
+    <t>ABRAHAM FRANCO NARES Y FAM.</t>
+  </si>
+  <si>
+    <t>1d9775302eb51dfdf82b58241619632d</t>
+  </si>
+  <si>
+    <t>FAM. DURAN ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>40cd525e13bc536b3210f0390a0892b0</t>
+  </si>
+  <si>
+    <t>FAM. HERNANDEZ RUIZ</t>
+  </si>
+  <si>
+    <t>aeecba369e15da89ea8d55fb7c93a8be</t>
+  </si>
+  <si>
+    <t>FAM. VERAZALUCE CAZARES</t>
+  </si>
+  <si>
+    <t>4affeba14c070365ae4c909729874864</t>
+  </si>
+  <si>
+    <t>FAM. HERNANDEZ VERAZALUCE</t>
+  </si>
+  <si>
+    <t>bbf61300c4cb02b85095bf33d724efda</t>
+  </si>
+  <si>
+    <t>FAM. BUENDIA VALENCIA</t>
+  </si>
+  <si>
+    <t>77f9d8baef41d9d4b7f384ec9988e044</t>
+  </si>
+  <si>
+    <t>FAM. AVILA BUENDIA</t>
+  </si>
+  <si>
+    <t>6c88a70210612156ea7e06a218358872</t>
+  </si>
+  <si>
+    <t>FAM. VERAZALUCE MARTINEZ</t>
+  </si>
+  <si>
+    <t>b932ffd8e054091d036d76cdad5eff7c</t>
+  </si>
+  <si>
+    <t>FAM. VALENCIA CORTES</t>
+  </si>
+  <si>
+    <t>76c7027cc4f01a8c5aedb4a8527ad2a3</t>
+  </si>
+  <si>
+    <t>LIC. MIRIAM CORTES Y FAMILIA</t>
+  </si>
+  <si>
+    <t>9de41efade00b59439f3a537625114f3</t>
+  </si>
+  <si>
+    <t>FAM. VARELA VALENCIA</t>
+  </si>
+  <si>
+    <t>88c9ab80bdc732a2d0d7a6fc4c57c912</t>
+  </si>
+  <si>
+    <t>FAM. DURAN DE VIANA</t>
+  </si>
+  <si>
+    <t>a652fae5c6ac9df6419b546bf309fc7b</t>
+  </si>
+  <si>
+    <t>FAM. DURAN MARTINEZ</t>
+  </si>
+  <si>
+    <t>dd17cc368df8b0a9391b3628b1c1be49</t>
+  </si>
+  <si>
+    <t>FAM. ESTRADA CASTRO</t>
+  </si>
+  <si>
+    <t>94160d122a4ff3692c579f7fe32d1906</t>
+  </si>
+  <si>
+    <t>FAM. HERNANDEZ CASTILLO</t>
+  </si>
+  <si>
+    <t>c6b3ef38a8c5c2ae65c6bfb774699d32</t>
+  </si>
+  <si>
+    <t>FAM. CRUZ VAZQUEZ</t>
+  </si>
+  <si>
+    <t>c5b7d34f5812457a0108b25b76347186</t>
+  </si>
+  <si>
+    <t>2c40f394312060501797845c077edff8</t>
+  </si>
+  <si>
+    <t>LIC. PICHARDO Y ESPOSA</t>
+  </si>
+  <si>
+    <t>f23a5339333a85bca1ce74cddf880827</t>
+  </si>
+  <si>
+    <t>CONTADORA NORMA</t>
+  </si>
+  <si>
+    <t>d0781acf478590f7f4209c2118027eca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LULU LOPEZ </t>
+  </si>
+  <si>
+    <t>b3400924f445da34302ff017b5179a47</t>
+  </si>
+  <si>
+    <t>DRA. DELIA FUENTES</t>
+  </si>
+  <si>
+    <t>870fb1212ee3527ea3220b774863c0f1</t>
+  </si>
+  <si>
+    <t>FAM. MENDOZA CEJA</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1599,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C74"/>
+  <dimension ref="A1:C102"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -2245,13 +2413,321 @@
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B74" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C74" s="1">
         <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B75" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B76" t="s">
+        <v>151</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" t="s">
+        <v>153</v>
+      </c>
+      <c r="C77" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78" t="s">
+        <v>155</v>
+      </c>
+      <c r="C78" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" t="s">
+        <v>159</v>
+      </c>
+      <c r="C80" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B81" t="s">
+        <v>161</v>
+      </c>
+      <c r="C81" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" t="s">
+        <v>163</v>
+      </c>
+      <c r="C82" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" t="s">
+        <v>165</v>
+      </c>
+      <c r="C83" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B84" t="s">
+        <v>167</v>
+      </c>
+      <c r="C84" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B85" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B86" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B87" t="s">
+        <v>173</v>
+      </c>
+      <c r="C87" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B88" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B89" t="s">
+        <v>177</v>
+      </c>
+      <c r="C89" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B90" t="s">
+        <v>179</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B91" t="s">
+        <v>181</v>
+      </c>
+      <c r="C91" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B92" t="s">
+        <v>183</v>
+      </c>
+      <c r="C92" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" t="s">
+        <v>185</v>
+      </c>
+      <c r="C93" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B94" t="s">
+        <v>187</v>
+      </c>
+      <c r="C94" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" t="s">
+        <v>189</v>
+      </c>
+      <c r="C95" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B96" t="s">
+        <v>191</v>
+      </c>
+      <c r="C96" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B98" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B99" t="s">
+        <v>196</v>
+      </c>
+      <c r="C99" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B100" t="s">
+        <v>198</v>
+      </c>
+      <c r="C100" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B101" t="s">
+        <v>200</v>
+      </c>
+      <c r="C101" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B102" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/invitados.xlsx
+++ b/assets/data/invitados.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11460"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="227">
   <si>
     <t>id</t>
   </si>
@@ -636,6 +636,78 @@
   </si>
   <si>
     <t>FAM. MENDOZA CEJA</t>
+  </si>
+  <si>
+    <t>322482c50de1a7c699ce41c291c5f3f9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM. VERAZALUCE PEREZ </t>
+  </si>
+  <si>
+    <t>157740eeab41954636955aa53f127f76</t>
+  </si>
+  <si>
+    <t>LIC. DANIEL VERAZALUCE Y FAM</t>
+  </si>
+  <si>
+    <t>435e217ae5a1b6c8f41443998d2ec050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM. CASTRO MORALES </t>
+  </si>
+  <si>
+    <t>ff83cef1bf672637e22b48c3377f6610</t>
+  </si>
+  <si>
+    <t>TERESA SIGUENZA Y FAMILIA</t>
+  </si>
+  <si>
+    <t>ad3eda1f9fdaadb8dbb7fec828603d02</t>
+  </si>
+  <si>
+    <t>FAM. GALICIA RAMOS</t>
+  </si>
+  <si>
+    <t>f17c54e5b3d18819eee1d112f8e0b4f0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAURICIO RAMOS Y FAM. </t>
+  </si>
+  <si>
+    <t>d95897b68fb83d586bc1e462fe2bca68</t>
+  </si>
+  <si>
+    <t>FAM. RAMIREZ JUAREZ</t>
+  </si>
+  <si>
+    <t>5e9254b5814d0721042ee3db328d7a71</t>
+  </si>
+  <si>
+    <t>FAM. MORALES ORTEGA</t>
+  </si>
+  <si>
+    <t>d1f7b3a5de49bf839f5ada91d7f69cef</t>
+  </si>
+  <si>
+    <t>FAM. PEREZ REVILLA</t>
+  </si>
+  <si>
+    <t>d53cf9289f0ca101cc771b96db0968bb</t>
+  </si>
+  <si>
+    <t>FAM . ANDRADE VALENCIA</t>
+  </si>
+  <si>
+    <t>ecfb15ef8e1621dfafb38f984bd5f533</t>
+  </si>
+  <si>
+    <t>FAM. SIGUENZA GALICIA</t>
+  </si>
+  <si>
+    <t>807ecca1c69d6a5195e5c8450bddea0f</t>
+  </si>
+  <si>
+    <t>FAM. QUIROZ GARCIA</t>
   </si>
 </sst>
 </file>
@@ -648,7 +720,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -658,6 +730,13 @@
     </font>
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1141,137 +1220,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1280,6 +1359,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1599,7 +1682,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C114"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -2730,6 +2813,138 @@
         <v>5</v>
       </c>
     </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C103" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="C104" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C105" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C108" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B112" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C112" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B113" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C113" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C114" s="5">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>

--- a/assets/data/invitados.xlsx
+++ b/assets/data/invitados.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="236">
   <si>
     <t>id</t>
   </si>
@@ -708,6 +708,33 @@
   </si>
   <si>
     <t>FAM. QUIROZ GARCIA</t>
+  </si>
+  <si>
+    <t>8e319cda2af8f5e54d826b5b8ee81d46</t>
+  </si>
+  <si>
+    <t>BRANDON ORTEGA</t>
+  </si>
+  <si>
+    <t>baf88f29434fdf7b92d1d07713c0cff3</t>
+  </si>
+  <si>
+    <t>ALEJANDRO RAMON</t>
+  </si>
+  <si>
+    <t>596df4e73045332331bfd21bc9fe9619</t>
+  </si>
+  <si>
+    <t>FAM. BENITEZ GARCIA</t>
+  </si>
+  <si>
+    <t>ef27ab062e4ad6c8ff5a62da1051cddd</t>
+  </si>
+  <si>
+    <t>24671525b891e104768c46c783d709c4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAM. BUENDIA SIGUENZA </t>
   </si>
 </sst>
 </file>
@@ -1350,7 +1377,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1359,6 +1386,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1682,7 +1713,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C119"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -2945,6 +2976,61 @@
         <v>4</v>
       </c>
     </row>
+    <row r="115" spans="1:3">
+      <c r="A115" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C115" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C116" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C117" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C118" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C119" s="7">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>

--- a/assets/data/invitados.xlsx
+++ b/assets/data/invitados.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="244">
   <si>
     <t>id</t>
   </si>
@@ -735,6 +735,30 @@
   </si>
   <si>
     <t xml:space="preserve">FAM. BUENDIA SIGUENZA </t>
+  </si>
+  <si>
+    <t>95120bae1db52cadd40ae032ba30acce</t>
+  </si>
+  <si>
+    <t>FAM.MARTINEZ DURAN</t>
+  </si>
+  <si>
+    <t>108ca2a51b832fe4cbe8b1cf5c318b34</t>
+  </si>
+  <si>
+    <t>SR. MIGUELITO Y ESPOSA</t>
+  </si>
+  <si>
+    <t>1bc837d31385d5f32e99a521b466e350</t>
+  </si>
+  <si>
+    <t>SRA. ROSALBA Y FAM.</t>
+  </si>
+  <si>
+    <t>1a5dd69223d3f02be540fcc2cda42d24</t>
+  </si>
+  <si>
+    <t>SR. OSCAR GONZALEZ Y FAM.</t>
   </si>
 </sst>
 </file>
@@ -1377,7 +1401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1390,16 +1414,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Coma" xfId="1" builtinId="3"/>
     <cellStyle name="Moneda" xfId="2" builtinId="4"/>
-    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
+    <cellStyle name="K" xfId="3" builtinId="5"/>
     <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
     <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
     <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
@@ -1713,7 +1740,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C119"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -2980,10 +3007,10 @@
       <c r="A115" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B115" s="6" t="s">
+      <c r="B115" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="5">
         <v>1</v>
       </c>
     </row>
@@ -2991,10 +3018,10 @@
       <c r="A116" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B116" s="6" t="s">
+      <c r="B116" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="C116" s="7">
+      <c r="C116" s="5">
         <v>1</v>
       </c>
     </row>
@@ -3002,10 +3029,10 @@
       <c r="A117" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B117" s="6" t="s">
+      <c r="B117" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="5">
         <v>4</v>
       </c>
     </row>
@@ -3013,10 +3040,10 @@
       <c r="A118" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B118" s="6" t="s">
+      <c r="B118" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="C118" s="7">
+      <c r="C118" s="5">
         <v>3</v>
       </c>
     </row>
@@ -3024,11 +3051,55 @@
       <c r="A119" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="5">
         <v>2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C120" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C121" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>241</v>
+      </c>
+      <c r="C122" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C123" s="7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/assets/data/invitados.xlsx
+++ b/assets/data/invitados.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="250">
   <si>
     <t>id</t>
   </si>
@@ -759,6 +759,24 @@
   </si>
   <si>
     <t>SR. OSCAR GONZALEZ Y FAM.</t>
+  </si>
+  <si>
+    <t>1a5dd69223d3f02be540fcc2cda42d24we</t>
+  </si>
+  <si>
+    <t>SRITA. BLANCA SORIANO</t>
+  </si>
+  <si>
+    <t>1a5dd69223d3f02be540fcc2cda42d24ws</t>
+  </si>
+  <si>
+    <t>SRITA. MIREYA FLORES</t>
+  </si>
+  <si>
+    <t>1a5dd69223d3f02be540fcc2cda42d24y</t>
+  </si>
+  <si>
+    <t>DOC. RICARDO CORTES</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1419,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1414,12 +1432,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1740,7 +1762,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C123"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="36" style="1" customWidth="1"/>
@@ -3102,6 +3124,39 @@
         <v>5</v>
       </c>
     </row>
+    <row r="124" spans="1:3">
+      <c r="A124" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="C124" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C126" s="10">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
